--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2022_o_higgins.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2022_o_higgins.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>27.88795389882818</v>
+      </c>
+      <c r="C2">
         <v>30.09174422529778</v>
-      </c>
-      <c r="C2">
-        <v>27.88795389882818</v>
       </c>
       <c r="D2">
         <v>3.32317060956311</v>
       </c>
       <c r="E2">
-        <v>19.04785525140986</v>
+        <v>17.65287200189254</v>
       </c>
       <c r="F2">
         <v>63.29927274669759</v>
       </c>
       <c r="G2">
-        <v>17.65287200189254</v>
+        <v>19.04785525140986</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>25.63541666666667</v>
+      </c>
+      <c r="C3">
         <v>31.61458333333333</v>
-      </c>
-      <c r="C3">
-        <v>25.63541666666667</v>
       </c>
       <c r="D3">
         <v>3.163097199341022</v>
       </c>
       <c r="E3">
-        <v>20.10466348701643</v>
+        <v>16.30233174350822</v>
       </c>
       <c r="F3">
         <v>63.59300476947536</v>
       </c>
       <c r="G3">
-        <v>16.30233174350822</v>
+        <v>20.10466348701643</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>28.56575288041319</v>
+      </c>
+      <c r="C4">
         <v>39.96821613031386</v>
-      </c>
-      <c r="C4">
-        <v>28.56575288041319</v>
       </c>
       <c r="D4">
         <v>2.501988071570576</v>
       </c>
       <c r="E4">
-        <v>23.71522866572371</v>
+        <v>16.94955209806695</v>
       </c>
       <c r="F4">
         <v>59.33521923620934</v>
       </c>
       <c r="G4">
-        <v>16.94955209806695</v>
+        <v>23.71522866572371</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>28.08738607110554</v>
+      </c>
+      <c r="C5">
         <v>34.44653169136576</v>
-      </c>
-      <c r="C5">
-        <v>28.08738607110554</v>
       </c>
       <c r="D5">
         <v>2.903049888911331</v>
       </c>
       <c r="E5">
-        <v>21.19344206155559</v>
+        <v>17.28093831599675</v>
       </c>
       <c r="F5">
         <v>61.52561962244767</v>
       </c>
       <c r="G5">
-        <v>17.28093831599675</v>
+        <v>21.19344206155559</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>29.4125893733352</v>
+      </c>
+      <c r="C6">
         <v>32.92443572129539</v>
-      </c>
-      <c r="C6">
-        <v>29.4125893733352</v>
       </c>
       <c r="D6">
         <v>3.03725782414307</v>
       </c>
       <c r="E6">
-        <v>20.28153201779006</v>
+        <v>18.11822617556889</v>
       </c>
       <c r="F6">
         <v>61.60024180664104</v>
       </c>
       <c r="G6">
-        <v>18.11822617556889</v>
+        <v>20.28153201779006</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>30.92060523631418</v>
+      </c>
+      <c r="C7">
         <v>27.85617137028222</v>
-      </c>
-      <c r="C7">
-        <v>30.92060523631418</v>
       </c>
       <c r="D7">
         <v>3.589868782422948</v>
       </c>
       <c r="E7">
-        <v>17.5442353508044</v>
+        <v>19.47426185186177</v>
       </c>
       <c r="F7">
         <v>62.98150279733383</v>
       </c>
       <c r="G7">
-        <v>19.47426185186177</v>
+        <v>17.5442353508044</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>28.91163911091646</v>
+      </c>
+      <c r="C8">
         <v>33.83882623453411</v>
-      </c>
-      <c r="C8">
-        <v>28.91163911091646</v>
       </c>
       <c r="D8">
         <v>2.95518524510597</v>
       </c>
       <c r="E8">
-        <v>20.79184607104413</v>
+        <v>17.76439720129171</v>
       </c>
       <c r="F8">
         <v>61.44375672766415</v>
       </c>
       <c r="G8">
-        <v>17.76439720129171</v>
+        <v>20.79184607104413</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>33.05388885773566</v>
+      </c>
+      <c r="C9">
         <v>24.86121235910952</v>
-      </c>
-      <c r="C9">
-        <v>33.05388885773566</v>
       </c>
       <c r="D9">
         <v>4.022329987594452</v>
       </c>
       <c r="E9">
-        <v>15.74340399843755</v>
+        <v>20.93142999183267</v>
       </c>
       <c r="F9">
         <v>63.32516600972976</v>
       </c>
       <c r="G9">
-        <v>20.93142999183267</v>
+        <v>15.74340399843755</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>27.16663064620705</v>
+      </c>
+      <c r="C10">
         <v>37.10827750162092</v>
-      </c>
-      <c r="C10">
-        <v>27.16663064620705</v>
       </c>
       <c r="D10">
         <v>2.694816540477577</v>
       </c>
       <c r="E10">
+        <v>16.53729772398369</v>
+      </c>
+      <c r="F10">
+        <v>60.8735692672017</v>
+      </c>
+      <c r="G10">
         <v>22.58913300881463</v>
-      </c>
-      <c r="F10">
-        <v>60.87356926720168</v>
-      </c>
-      <c r="G10">
-        <v>16.53729772398368</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>30.40970096538733</v>
+      </c>
+      <c r="C11">
         <v>31.6105486225571</v>
-      </c>
-      <c r="C11">
-        <v>30.40970096538733</v>
       </c>
       <c r="D11">
         <v>3.163500931098696</v>
       </c>
       <c r="E11">
-        <v>19.51024560383665</v>
+        <v>18.76907426246185</v>
       </c>
       <c r="F11">
         <v>61.72068013370149</v>
       </c>
       <c r="G11">
-        <v>18.76907426246185</v>
+        <v>19.51024560383665</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>28.83038411739318</v>
+      </c>
+      <c r="C12">
         <v>31.75442382391023</v>
-      </c>
-      <c r="C12">
-        <v>28.83038411739318</v>
       </c>
       <c r="D12">
         <v>3.149167516139993</v>
       </c>
       <c r="E12">
-        <v>19.7742390647047</v>
+        <v>17.95336961634079</v>
       </c>
       <c r="F12">
         <v>62.27239131895451</v>
       </c>
       <c r="G12">
-        <v>17.95336961634079</v>
+        <v>19.7742390647047</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>27.67035466859684</v>
+      </c>
+      <c r="C13">
         <v>35.28073622169372</v>
-      </c>
-      <c r="C13">
-        <v>27.67035466859684</v>
       </c>
       <c r="D13">
         <v>2.834407971864009</v>
       </c>
       <c r="E13">
-        <v>21.65111999492353</v>
+        <v>16.98077289168094</v>
       </c>
       <c r="F13">
         <v>61.36810711339552</v>
       </c>
       <c r="G13">
-        <v>16.98077289168094</v>
+        <v>21.65111999492353</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>27.54536481664262</v>
+      </c>
+      <c r="C14">
         <v>37.02831979348569</v>
-      </c>
-      <c r="C14">
-        <v>27.54536481664262</v>
       </c>
       <c r="D14">
         <v>2.700635636661882</v>
       </c>
       <c r="E14">
-        <v>22.49953866026942</v>
+        <v>16.73740542535523</v>
       </c>
       <c r="F14">
         <v>60.76305591437534</v>
       </c>
       <c r="G14">
-        <v>16.73740542535523</v>
+        <v>22.49953866026942</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>26.27791300666737</v>
+      </c>
+      <c r="C15">
         <v>34.22584400465658</v>
-      </c>
-      <c r="C15">
-        <v>26.27791300666737</v>
       </c>
       <c r="D15">
         <v>2.921768707482993</v>
       </c>
       <c r="E15">
-        <v>21.32401424238428</v>
+        <v>16.37214822629566</v>
       </c>
       <c r="F15">
         <v>62.30383753132006</v>
       </c>
       <c r="G15">
-        <v>16.37214822629566</v>
+        <v>21.32401424238428</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>30.10603290676417</v>
+      </c>
+      <c r="C16">
         <v>30.9079829372334</v>
-      </c>
-      <c r="C16">
-        <v>30.10603290676417</v>
       </c>
       <c r="D16">
         <v>3.235410094637224</v>
       </c>
       <c r="E16">
-        <v>19.19583383795567</v>
+        <v>18.69777158774373</v>
       </c>
       <c r="F16">
         <v>62.10639457430059</v>
       </c>
       <c r="G16">
-        <v>18.69777158774373</v>
+        <v>19.19583383795567</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>26.60918480265585</v>
+      </c>
+      <c r="C17">
         <v>25.95905569900406</v>
-      </c>
-      <c r="C17">
-        <v>26.60918480265585</v>
       </c>
       <c r="D17">
         <v>3.852220248667851</v>
       </c>
       <c r="E17">
-        <v>17.01471788207562</v>
+        <v>17.44084136722173</v>
       </c>
       <c r="F17">
-        <v>65.54444075070266</v>
+        <v>65.54444075070265</v>
       </c>
       <c r="G17">
-        <v>17.44084136722174</v>
+        <v>17.01471788207561</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>28.66040533860603</v>
+      </c>
+      <c r="C18">
         <v>37.46910528917449</v>
-      </c>
-      <c r="C18">
-        <v>28.66040533860603</v>
       </c>
       <c r="D18">
         <v>2.668865435356201</v>
       </c>
       <c r="E18">
-        <v>22.55415377291121</v>
+        <v>17.25184479885742</v>
       </c>
       <c r="F18">
         <v>60.19400142823137</v>
       </c>
       <c r="G18">
-        <v>17.25184479885742</v>
+        <v>22.55415377291121</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>26.82215743440233</v>
+      </c>
+      <c r="C19">
         <v>33.04630822428639</v>
-      </c>
-      <c r="C19">
-        <v>26.82215743440233</v>
       </c>
       <c r="D19">
         <v>3.02605662700041</v>
       </c>
       <c r="E19">
-        <v>20.67093600237499</v>
+        <v>16.77764112133679</v>
       </c>
       <c r="F19">
-        <v>62.55142287628822</v>
+        <v>62.55142287628823</v>
       </c>
       <c r="G19">
-        <v>16.77764112133678</v>
+        <v>20.670936002375</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>28.70753935376968</v>
+      </c>
+      <c r="C20">
         <v>48.63297431648716</v>
-      </c>
-      <c r="C20">
-        <v>28.70753935376968</v>
       </c>
       <c r="D20">
         <v>2.056218057921635</v>
       </c>
       <c r="E20">
-        <v>27.42349918243401</v>
+        <v>16.18780658724597</v>
       </c>
       <c r="F20">
         <v>56.38869423032002</v>
       </c>
       <c r="G20">
-        <v>16.18780658724597</v>
+        <v>27.42349918243401</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>29.50120526608567</v>
+      </c>
+      <c r="C21">
         <v>39.73669571666976</v>
-      </c>
-      <c r="C21">
-        <v>29.50120526608567</v>
       </c>
       <c r="D21">
         <v>2.516565562295847</v>
       </c>
       <c r="E21">
-        <v>23.47978525254738</v>
+        <v>17.43179577078996</v>
       </c>
       <c r="F21">
         <v>59.08841897666264</v>
       </c>
       <c r="G21">
-        <v>17.43179577078996</v>
+        <v>23.47978525254738</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>24.33972035214915</v>
+      </c>
+      <c r="C22">
         <v>38.63283272915588</v>
-      </c>
-      <c r="C22">
-        <v>24.33972035214915</v>
       </c>
       <c r="D22">
         <v>2.588471849865952</v>
       </c>
       <c r="E22">
+        <v>14.93485859548777</v>
+      </c>
+      <c r="F22">
+        <v>61.36002542103591</v>
+      </c>
+      <c r="G22">
         <v>23.70511598347633</v>
-      </c>
-      <c r="F22">
-        <v>61.3600254210359</v>
-      </c>
-      <c r="G22">
-        <v>14.93485859548776</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>30.92046470062556</v>
+      </c>
+      <c r="C23">
         <v>52.25647899910634</v>
-      </c>
-      <c r="C23">
-        <v>30.92046470062556</v>
       </c>
       <c r="D23">
         <v>1.91363830696879</v>
       </c>
       <c r="E23">
-        <v>28.52786925234784</v>
+        <v>16.88010733016221</v>
       </c>
       <c r="F23">
         <v>54.59202341748993</v>
       </c>
       <c r="G23">
-        <v>16.88010733016221</v>
+        <v>28.52786925234784</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>25.18500835521604</v>
+      </c>
+      <c r="C24">
         <v>48.43638099785151</v>
-      </c>
-      <c r="C24">
-        <v>25.18500835521604</v>
       </c>
       <c r="D24">
         <v>2.06456382454411</v>
       </c>
       <c r="E24">
-        <v>27.89770383610614</v>
+        <v>14.50570603602365</v>
       </c>
       <c r="F24">
         <v>57.5965901278702</v>
       </c>
       <c r="G24">
-        <v>14.50570603602365</v>
+        <v>27.89770383610614</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>28.93122999190033</v>
+      </c>
+      <c r="C25">
         <v>31.43826898599915</v>
-      </c>
-      <c r="C25">
-        <v>28.93122999190033</v>
       </c>
       <c r="D25">
         <v>3.180836707152497</v>
       </c>
       <c r="E25">
-        <v>19.60364607133409</v>
+        <v>18.04035691094062</v>
       </c>
       <c r="F25">
         <v>62.3559970177253</v>
       </c>
       <c r="G25">
-        <v>18.04035691094062</v>
+        <v>19.60364607133409</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>29.70959732268164</v>
+      </c>
+      <c r="C26">
         <v>40.28932311346216</v>
-      </c>
-      <c r="C26">
-        <v>29.70959732268164</v>
       </c>
       <c r="D26">
         <v>2.482047159699893</v>
       </c>
       <c r="E26">
-        <v>23.69975233377786</v>
+        <v>17.47634470057789</v>
       </c>
       <c r="F26">
         <v>58.82390296564424</v>
       </c>
       <c r="G26">
-        <v>17.47634470057789</v>
+        <v>23.69975233377786</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>28.54635261460587</v>
+      </c>
+      <c r="C27">
         <v>32.88974160101237</v>
-      </c>
-      <c r="C27">
-        <v>28.54635261460587</v>
       </c>
       <c r="D27">
         <v>3.040461710314013</v>
       </c>
       <c r="E27">
-        <v>20.37322679343566</v>
+        <v>17.68275722557969</v>
       </c>
       <c r="F27">
         <v>61.94401598098466</v>
       </c>
       <c r="G27">
-        <v>17.68275722557969</v>
+        <v>20.37322679343566</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>27.43556138051551</v>
+      </c>
+      <c r="C28">
         <v>42.87898645696811</v>
-      </c>
-      <c r="C28">
-        <v>27.43556138051551</v>
       </c>
       <c r="D28">
         <v>2.332144676515537</v>
       </c>
       <c r="E28">
-        <v>25.17634987815826</v>
+        <v>16.10875977940233</v>
       </c>
       <c r="F28">
         <v>58.7148903424394</v>
       </c>
       <c r="G28">
-        <v>16.10875977940233</v>
+        <v>25.17634987815826</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>29.08069189568882</v>
+      </c>
+      <c r="C29">
         <v>34.48941961541838</v>
-      </c>
-      <c r="C29">
-        <v>29.08069189568882</v>
       </c>
       <c r="D29">
         <v>2.899439918533605</v>
       </c>
       <c r="E29">
+        <v>17.77873208438456</v>
+      </c>
+      <c r="F29">
+        <v>61.13586343872457</v>
+      </c>
+      <c r="G29">
         <v>21.08540447689087</v>
-      </c>
-      <c r="F29">
-        <v>61.13586343872456</v>
-      </c>
-      <c r="G29">
-        <v>17.77873208438456</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>26.07913669064748</v>
+      </c>
+      <c r="C30">
         <v>38.00102774922919</v>
-      </c>
-      <c r="C30">
-        <v>26.07913669064748</v>
       </c>
       <c r="D30">
         <v>2.631507775524003</v>
       </c>
       <c r="E30">
-        <v>23.16003758221109</v>
+        <v>15.89414343877231</v>
       </c>
       <c r="F30">
         <v>60.94581897901659</v>
       </c>
       <c r="G30">
-        <v>15.89414343877231</v>
+        <v>23.16003758221109</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>25.06560039985006</v>
+      </c>
+      <c r="C31">
         <v>36.88616768711733</v>
-      </c>
-      <c r="C31">
-        <v>25.06560039985006</v>
       </c>
       <c r="D31">
         <v>2.711043360433604</v>
       </c>
       <c r="E31">
-        <v>22.7760203687987</v>
+        <v>15.47720083326904</v>
       </c>
       <c r="F31">
         <v>61.74677879793227</v>
       </c>
       <c r="G31">
-        <v>15.47720083326904</v>
+        <v>22.7760203687987</v>
       </c>
     </row>
     <row r="32">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="B32">
+        <v>26.70401493930906</v>
+      </c>
+      <c r="C32">
         <v>33.62900715841892</v>
-      </c>
-      <c r="C32">
-        <v>26.70401493930906</v>
       </c>
       <c r="D32">
         <v>2.973623322535863</v>
       </c>
       <c r="E32">
+        <v>16.6553431039503</v>
+      </c>
+      <c r="F32">
+        <v>62.370183441716</v>
+      </c>
+      <c r="G32">
         <v>20.97447345433369</v>
-      </c>
-      <c r="F32">
-        <v>62.37018344171601</v>
-      </c>
-      <c r="G32">
-        <v>16.65534310395031</v>
       </c>
     </row>
     <row r="33">
@@ -1173,22 +1173,22 @@
         </is>
       </c>
       <c r="B33">
+        <v>27.98145806995365</v>
+      </c>
+      <c r="C33">
         <v>50.31605562579014</v>
-      </c>
-      <c r="C33">
-        <v>27.98145806995365</v>
       </c>
       <c r="D33">
         <v>1.987437185929648</v>
       </c>
       <c r="E33">
-        <v>28.22027889387851</v>
+        <v>15.69368943512172</v>
       </c>
       <c r="F33">
         <v>56.08603167099976</v>
       </c>
       <c r="G33">
-        <v>15.69368943512172</v>
+        <v>28.22027889387851</v>
       </c>
     </row>
     <row r="34">
@@ -1198,22 +1198,22 @@
         </is>
       </c>
       <c r="B34">
+        <v>27.1326402713264</v>
+      </c>
+      <c r="C34">
         <v>33.36282533362825</v>
-      </c>
-      <c r="C34">
-        <v>27.1326402713264</v>
       </c>
       <c r="D34">
         <v>2.997348066298342</v>
       </c>
       <c r="E34">
-        <v>20.78739434031606</v>
+        <v>16.90554943035648</v>
       </c>
       <c r="F34">
         <v>62.30705622932745</v>
       </c>
       <c r="G34">
-        <v>16.90554943035648</v>
+        <v>20.78739434031606</v>
       </c>
     </row>
   </sheetData>
